--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0174.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0174.xlsx
@@ -2264,7 +2264,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Soạn thánh ca, điều chỉnh Tiếng Vang, và chỉ huy dàn nhạc Vox Sancti trình diễn tác phẩm một cách hoàn hảo—đó là nhiệm vụ của nhạc trưởng trưởng.</t>
+          <t>Soạn thánh ca, điều chỉnh Echo, và chỉ huy dàn nhạc Vox Sancti trình diễn tác phẩm một cách hoàn hảo—đó là nhiệm vụ của nhạc trưởng trưởng.</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Đồ ngốc! Cậu có biết phải vượt qua bao nhiêu thủ tục rườm rà mới xin được một con Exoswarm để thí nghiệm không?</t>
+          <t>Đồ ngốc! Mày có biết phải vượt qua bao nhiêu thủ tục rườm rà mới xin được một con Exoswarm để thí nghiệm không?</t>
         </is>
       </c>
     </row>
@@ -8179,7 +8179,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Hồi đó ta lạc mất tiêu luôn. Thật sự tưởng mình xong đời rồi.</t>
+          <t>Hồi đó tao lạc mất tiêu luôn. Thật sự tưởng mình xong đời rồi.</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Hồi đó ta lạc mất tiêu luôn. Thật sự tưởng mình xong đời rồi.</t>
+          <t>Hồi đó tao lạc mất tiêu luôn. Thật sự tưởng mình xong đời rồi.</t>
         </is>
       </c>
     </row>
@@ -8894,7 +8894,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Ngươi mù à? Ai ngu đến mức đi cướp trạm của Spacetrek Collective chứ?</t>
+          <t>Mày mù à? Ai ngu đến mức đi cướp trạm của Spacetrek Collective chứ?</t>
         </is>
       </c>
     </row>
@@ -9544,7 +9544,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Rồi đột nhiên, có cả đàn thứ tròn tròn, mập mập, phát sáng lấp lánh... nhảy nhót khắp xe của ta. Kỳ lạ đến mức ta đứng hình luôn.</t>
+          <t>Rồi đột nhiên, có cả đàn thứ tròn tròn, mập mập, phát sáng lấp lánh... nhảy nhót khắp xe của tao. Kỳ lạ đến mức tao đứng hình luôn.</t>
         </is>
       </c>
     </row>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Đứng im! Ta sẽ tống ngươi về Học Viện ngay! Đây là lãnh địa của ta!</t>
+          <t>Đứng im! Tao sẽ tống mày về Học Viện ngay! Đây là lãnh địa của tao!</t>
         </is>
       </c>
     </row>
@@ -9934,7 +9934,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Ta méc ông trưởng ga cho xem!</t>
+          <t>Tao méc ông trưởng ga cho xem!</t>
         </is>
       </c>
     </row>
@@ -10714,7 +10714,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Ui, lại thua nữa rồi. Mấy cái luật lệ này ta vẫn chưa ngấm nổi.</t>
+          <t>Ui, lại thua nữa rồi. Mấy cái luật lệ này tao vẫn chưa ngấm nổi.</t>
         </is>
       </c>
     </row>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Cậu cần luyện tập thêm. Và không chỉ với riêng ta đâu.</t>
+          <t>Cậu cần luyện tập thêm. Và không chỉ với riêng tao đâu.</t>
         </is>
       </c>
     </row>
@@ -10844,7 +10844,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Ui, lại thua nữa rồi. Mấy cái luật lệ này ta vẫn chưa ngấm nổi.</t>
+          <t>Ui, lại thua nữa rồi. Mấy cái luật lệ này tao vẫn chưa ngấm nổi.</t>
         </is>
       </c>
     </row>
@@ -10909,7 +10909,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Cậu cần luyện tập thêm. Và không chỉ với riêng ta đâu.</t>
+          <t>Cậu cần luyện tập thêm. Và không chỉ với riêng tao đâu.</t>
         </is>
       </c>
     </row>
@@ -11689,7 +11689,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Của ta cũng chẳng khá hơn. Lúc nào cũng bận việc cho bọn Solsworn, chẳng bao giờ rảnh lo chuyện nhà.</t>
+          <t>Của tao cũng chẳng khá hơn. Lúc nào cũng bận việc cho bọn Solsworn, chẳng bao giờ rảnh lo chuyện nhà.</t>
         </is>
       </c>
     </row>
@@ -11884,7 +11884,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Gì? Cậu muốn xin việc ở đây à? Còn lâu mới đủ đấy.</t>
+          <t>Gì? Mày muốn xin việc ở đây à? Còn lâu mới đủ đấy.</t>
         </is>
       </c>
     </row>
@@ -15004,7 +15004,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Ta cũng nghe rồi! Hắn chém chúng như Exostrider chém bơ vậy!</t>
+          <t>Tao cũng nghe rồi! Hắn chém chúng như Exostrider chém bơ vậy!</t>
         </is>
       </c>
     </row>
@@ -15459,7 +15459,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Lại là cậu? Ta bảo đừng có quay lại cho đến khi cậu giỏi lên mà!</t>
+          <t>Lại là cậu? Tao bảo đừng có quay lại cho đến khi cậu giỏi lên mà!</t>
         </is>
       </c>
     </row>
@@ -15524,7 +15524,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Chơi với mấy tay gà chỉ tổ làm hỏng phong độ của ta thôi!</t>
+          <t>Chơi với mấy tay gà chỉ tổ làm hỏng phong độ của tao thôi!</t>
         </is>
       </c>
     </row>
@@ -15589,7 +15589,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Ta hoàn toàn đồng ý với cậu! Tiếp đi, kể thêm cho ta nghe ta tuyệt vời thế nào nào!</t>
+          <t>Tao hoàn toàn đồng ý với cậu! Tiếp đi, kể thêm cho tao nghe tao tuyệt vời thế nào nào!</t>
         </is>
       </c>
     </row>
@@ -15654,7 +15654,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Lại một kẻ thách đấu à? Ta cá là ngươi không trụ nổi hai hiệp đâu.</t>
+          <t>Lại một kẻ thách đấu à? Tao cá là mày không trụ nổi hai hiệp đâu.</t>
         </is>
       </c>
     </row>
@@ -24949,7 +24949,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Cậu không thể... đợi được sao?</t>
+          <t>bạn không thể... đợi được sao?</t>
         </is>
       </c>
     </row>
@@ -30409,7 +30409,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Nó khiến ta nhớ đến thanh kiếm của Ephor Augusta chém xuyên qua những ngọn núi ở bãi săn. Nó đã thực sự khai sinh một tương lai mới cho Rinascita.</t>
+          <t>Nó khiến tao nhớ đến thanh kiếm của Ephor Augusta chém xuyên qua những ngọn núi ở bãi săn. Nó đã thực sự khai sinh một tương lai mới cho Rinascita.</t>
         </is>
       </c>
     </row>
@@ -30539,7 +30539,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Giờ thì lạnh sống lưng thật đấy. Nhưng ta tò mò hơn muốn biết cần bao nhiêu năng lượng để tạo ra kỳ quan này.</t>
+          <t>Giờ thì lạnh sống lưng thật đấy. Nhưng tao tò mò hơn muốn biết cần bao nhiêu năng lượng để tạo ra kỳ quan này.</t>
         </is>
       </c>
     </row>
